--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -61345,6 +61345,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2652">
+      <c r="A2652" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2652" t="n">
+        <v>164</v>
+      </c>
+      <c r="C2652" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="D2652" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="E2652" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="F2652" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="G2652" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -61368,6 +61368,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2653">
+      <c r="A2653" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2653" t="n">
+        <v>1670</v>
+      </c>
+      <c r="C2653" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="D2653" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="E2653" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="F2653" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="G2653" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -61391,6 +61391,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2654">
+      <c r="A2654" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2654" t="n">
+        <v>5100</v>
+      </c>
+      <c r="C2654" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="D2654" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="E2654" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F2654" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="G2654" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -61414,6 +61414,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2655">
+      <c r="A2655" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2655" t="n">
+        <v>566</v>
+      </c>
+      <c r="C2655" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="D2655" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="E2655" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="F2655" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="G2655" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -61255,19 +61255,19 @@
     </row>
     <row r="2648">
       <c r="A2648" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2648" t="n">
-        <v>5851</v>
+        <v>2447</v>
       </c>
       <c r="C2648" t="n">
-        <v>2.86999988555908</v>
+        <v>2.89000010490417</v>
       </c>
       <c r="D2648" t="n">
-        <v>2.8199999332428</v>
+        <v>2.84999990463257</v>
       </c>
       <c r="E2648" t="n">
-        <v>2.8199999332428</v>
+        <v>2.84999990463257</v>
       </c>
       <c r="F2648" t="n">
         <v>2.85999989509583</v>
@@ -61278,22 +61278,22 @@
     </row>
     <row r="2649">
       <c r="A2649" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2649" t="n">
-        <v>9808</v>
+        <v>5851</v>
       </c>
       <c r="C2649" t="n">
-        <v>2.84999990463257</v>
+        <v>2.86999988555908</v>
       </c>
       <c r="D2649" t="n">
-        <v>2.79999995231628</v>
+        <v>2.8199999332428</v>
       </c>
       <c r="E2649" t="n">
         <v>2.8199999332428</v>
       </c>
       <c r="F2649" t="n">
-        <v>2.79999995231628</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="G2649" t="s">
         <v>7</v>
@@ -61301,22 +61301,22 @@
     </row>
     <row r="2650">
       <c r="A2650" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2650" t="n">
-        <v>1000</v>
+        <v>9808</v>
       </c>
       <c r="C2650" t="n">
-        <v>2.78999996185303</v>
+        <v>2.84999990463257</v>
       </c>
       <c r="D2650" t="n">
-        <v>2.78999996185303</v>
+        <v>2.79999995231628</v>
       </c>
       <c r="E2650" t="n">
-        <v>2.78999996185303</v>
+        <v>2.8199999332428</v>
       </c>
       <c r="F2650" t="n">
-        <v>2.78999996185303</v>
+        <v>2.79999995231628</v>
       </c>
       <c r="G2650" t="s">
         <v>7</v>
@@ -61324,10 +61324,10 @@
     </row>
     <row r="2651">
       <c r="A2651" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2651" t="n">
-        <v>113</v>
+        <v>1000</v>
       </c>
       <c r="C2651" t="n">
         <v>2.78999996185303</v>
@@ -61347,22 +61347,22 @@
     </row>
     <row r="2652">
       <c r="A2652" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2652" t="n">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="C2652" t="n">
         <v>2.78999996185303</v>
       </c>
       <c r="D2652" t="n">
-        <v>2.76999998092651</v>
+        <v>2.78999996185303</v>
       </c>
       <c r="E2652" t="n">
         <v>2.78999996185303</v>
       </c>
       <c r="F2652" t="n">
-        <v>2.76999998092651</v>
+        <v>2.78999996185303</v>
       </c>
       <c r="G2652" t="s">
         <v>7</v>
@@ -61370,19 +61370,19 @@
     </row>
     <row r="2653">
       <c r="A2653" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2653" t="n">
-        <v>1670</v>
+        <v>164</v>
       </c>
       <c r="C2653" t="n">
-        <v>2.76999998092651</v>
+        <v>2.78999996185303</v>
       </c>
       <c r="D2653" t="n">
         <v>2.76999998092651</v>
       </c>
       <c r="E2653" t="n">
-        <v>2.76999998092651</v>
+        <v>2.78999996185303</v>
       </c>
       <c r="F2653" t="n">
         <v>2.76999998092651</v>
@@ -61393,22 +61393,22 @@
     </row>
     <row r="2654">
       <c r="A2654" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2654" t="n">
-        <v>5100</v>
+        <v>1670</v>
       </c>
       <c r="C2654" t="n">
-        <v>2.78999996185303</v>
+        <v>2.76999998092651</v>
       </c>
       <c r="D2654" t="n">
-        <v>2.70000004768372</v>
+        <v>2.76999998092651</v>
       </c>
       <c r="E2654" t="n">
-        <v>2.77999997138977</v>
+        <v>2.76999998092651</v>
       </c>
       <c r="F2654" t="n">
-        <v>2.77999997138977</v>
+        <v>2.76999998092651</v>
       </c>
       <c r="G2654" t="s">
         <v>7</v>
@@ -61416,24 +61416,47 @@
     </row>
     <row r="2655">
       <c r="A2655" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2655" t="n">
-        <v>566</v>
+        <v>5100</v>
       </c>
       <c r="C2655" t="n">
-        <v>2.8199999332428</v>
+        <v>2.78999996185303</v>
       </c>
       <c r="D2655" t="n">
-        <v>2.74000000953674</v>
+        <v>2.70000004768372</v>
       </c>
       <c r="E2655" t="n">
-        <v>2.74000000953674</v>
+        <v>2.77999997138977</v>
       </c>
       <c r="F2655" t="n">
-        <v>2.79999995231628</v>
+        <v>2.77999997138977</v>
       </c>
       <c r="G2655" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2656">
+      <c r="A2656" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2656" t="n">
+        <v>5398</v>
+      </c>
+      <c r="C2656" t="n">
+        <v>2.82999992370605</v>
+      </c>
+      <c r="D2656" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="E2656" t="n">
+        <v>2.82999992370605</v>
+      </c>
+      <c r="F2656" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="G2656" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -69483,6 +69483,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2659">
+      <c r="A2659" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2659" t="n">
+        <v>12388</v>
+      </c>
+      <c r="C2659" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="D2659" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="E2659" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="F2659" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="G2659" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="H2659" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -69509,6 +69509,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2660">
+      <c r="A2660" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2660" t="n">
+        <v>623</v>
+      </c>
+      <c r="C2660" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="D2660" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="E2660" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="F2660" t="n">
+        <v>2.80999994277954</v>
+      </c>
+      <c r="G2660" t="n">
+        <v>2.80999994277954</v>
+      </c>
+      <c r="H2660" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -69517,7 +69517,7 @@
         <v>623</v>
       </c>
       <c r="C2660" t="n">
-        <v>2.79999995231628</v>
+        <v>2.80999994277954</v>
       </c>
       <c r="D2660" t="n">
         <v>2.73000001907349</v>
@@ -69532,6 +69532,32 @@
         <v>2.80999994277954</v>
       </c>
       <c r="H2660" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2661">
+      <c r="A2661" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2661" t="n">
+        <v>2158</v>
+      </c>
+      <c r="C2661" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="D2661" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="E2661" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="F2661" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="G2661" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="H2661" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -69561,6 +69561,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2662">
+      <c r="A2662" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2662" t="n">
+        <v>2622</v>
+      </c>
+      <c r="C2662" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="D2662" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="E2662" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F2662" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="G2662" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="H2662" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -69639,6 +69639,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2665">
+      <c r="A2665" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2665" t="n">
+        <v>1330</v>
+      </c>
+      <c r="C2665" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="D2665" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="E2665" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F2665" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="G2665" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="H2665" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -61729,8 +61729,31 @@
       <c r="E2668" t="n">
         <v>2.71000003814697</v>
       </c>
-      <c r="F2668"/>
+      <c r="F2668" t="n">
+        <v>2.76999998092651</v>
+      </c>
       <c r="G2668" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2669">
+      <c r="A2669" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2669" t="n">
+        <v>3404</v>
+      </c>
+      <c r="C2669" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="D2669" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="E2669" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="F2669"/>
+      <c r="G2669" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -61752,8 +61752,31 @@
       <c r="E2669" t="n">
         <v>2.76999998092651</v>
       </c>
-      <c r="F2669"/>
+      <c r="F2669" t="n">
+        <v>2.75999999046326</v>
+      </c>
       <c r="G2669" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2670">
+      <c r="A2670" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2670" t="n">
+        <v>134</v>
+      </c>
+      <c r="C2670" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="D2670" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="E2670" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="F2670"/>
+      <c r="G2670" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -61775,8 +61775,31 @@
       <c r="E2670" t="n">
         <v>2.74000000953674</v>
       </c>
-      <c r="F2670"/>
+      <c r="F2670" t="n">
+        <v>2.74000000953674</v>
+      </c>
       <c r="G2670" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2671">
+      <c r="A2671" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2671" t="n">
+        <v>664</v>
+      </c>
+      <c r="C2671" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D2671" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="E2671" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="F2671"/>
+      <c r="G2671" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -61798,8 +61798,31 @@
       <c r="E2671" t="n">
         <v>2.8199999332428</v>
       </c>
-      <c r="F2671"/>
+      <c r="F2671" t="n">
+        <v>2.85999989509583</v>
+      </c>
       <c r="G2671" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2672">
+      <c r="A2672" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2672" t="n">
+        <v>9599</v>
+      </c>
+      <c r="C2672" t="n">
+        <v>2.80999994277954</v>
+      </c>
+      <c r="D2672" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="E2672" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="F2672"/>
+      <c r="G2672" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -61828,6 +61828,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2673">
+      <c r="A2673" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2673" t="n">
+        <v>656</v>
+      </c>
+      <c r="C2673" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="D2673" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="E2673" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="F2673" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="G2673" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -69925,6 +69925,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2676">
+      <c r="A2676" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2676" t="n">
+        <v>13529</v>
+      </c>
+      <c r="C2676" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="D2676" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2676" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="F2676" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="G2676" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="H2676" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -69933,7 +69933,7 @@
         <v>13529</v>
       </c>
       <c r="C2676" t="n">
-        <v>2.77999997138977</v>
+        <v>2.79999995231628</v>
       </c>
       <c r="D2676" t="n">
         <v>2.66000008583069</v>
@@ -69948,6 +69948,32 @@
         <v>2.79999995231628</v>
       </c>
       <c r="H2676" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2677">
+      <c r="A2677" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2677" t="n">
+        <v>594</v>
+      </c>
+      <c r="C2677" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="D2677" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="E2677" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="F2677" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G2677" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H2677" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -78040,6 +78040,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2679">
+      <c r="A2679" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2679" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2679" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D2679" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="E2679" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F2679" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G2679" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="H2679" t="n">
+        <v>2484</v>
+      </c>
+      <c r="I2679" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -78069,6 +78069,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2680">
+      <c r="A2680" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2680" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2680" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="D2680" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="E2680" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F2680" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G2680" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="H2680" t="n">
+        <v>1855</v>
+      </c>
+      <c r="I2680" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -78098,6 +78098,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2681">
+      <c r="A2681" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2681" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2681" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D2681" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2681" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F2681" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="G2681" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="H2681" t="n">
+        <v>2791</v>
+      </c>
+      <c r="I2681" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -78109,7 +78109,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="D2681" t="n">
-        <v>2.66000008583069</v>
+        <v>2.72000002861023</v>
       </c>
       <c r="E2681" t="n">
         <v>2.66000008583069</v>
@@ -78124,6 +78124,35 @@
         <v>2791</v>
       </c>
       <c r="I2681" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2682">
+      <c r="A2682" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2682" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2682" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="D2682" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="E2682" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="F2682" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="G2682" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="H2682" t="n">
+        <v>4308</v>
+      </c>
+      <c r="I2682" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -78156,6 +78156,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2683">
+      <c r="A2683" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2683" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2683" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D2683" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="E2683" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="F2683" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="G2683" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="H2683" t="n">
+        <v>4588</v>
+      </c>
+      <c r="I2683" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -78185,6 +78185,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2684">
+      <c r="A2684" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2684" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2684" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="D2684" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="E2684" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="F2684" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="G2684" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="H2684" t="n">
+        <v>20290</v>
+      </c>
+      <c r="I2684" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -78214,6 +78214,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2685">
+      <c r="A2685" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2685" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2685" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="D2685" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="E2685" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2685" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="G2685" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="H2685" t="n">
+        <v>6389</v>
+      </c>
+      <c r="I2685" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -78243,6 +78243,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2686">
+      <c r="A2686" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2686" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2686" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="D2686" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="E2686" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F2686" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="G2686" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="H2686" t="n">
+        <v>3250</v>
+      </c>
+      <c r="I2686" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABT.MI.xlsx
+++ b/data/ABT.MI.xlsx
@@ -78272,6 +78272,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2687">
+      <c r="A2687" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2687" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2687" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="D2687" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="E2687" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="F2687" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="G2687" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="H2687" t="n">
+        <v>547</v>
+      </c>
+      <c r="I2687" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
